--- a/san/brocade01_audit.xlsx
+++ b/san/brocade01_audit.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 13:28</t>
+          <t>2026-06-09 14:54</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
